--- a/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
+++ b/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
@@ -55,7 +55,7 @@
     <x:t>Cantidad_Real</x:t>
   </x:si>
   <x:si>
-    <x:t>1043</x:t>
+    <x:t>1045</x:t>
   </x:si>
   <x:si>
     <x:t>00604</x:t>
@@ -67,121 +67,25 @@
     <x:t xml:space="preserve">Master    </x:t>
   </x:si>
   <x:si>
-    <x:t>12405041</x:t>
+    <x:t>12504010</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SU             </x:t>
   </x:si>
   <x:si>
-    <x:t>02102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI-757/60 PP CAVITATED TC8 AP901 WG62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12504141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12448010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03817</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI-757/60 PP CAVITATED TC8 RP1001 WG62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12445030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coated 80 RP 3000 WG62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12500140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08126</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Papel Metalizado plata brillo AP 903 SK60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12554172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08886</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thermal Easytop AP903 SK60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12440101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08888</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOP TRANSFER. AP903 SK60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12900144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08923</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI-7093/60 PP Gloss White TC8 AP903 PET 30- Film</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12998041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coated 80 RP3000 WG74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12447100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09524</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI-757/66 PP CAVITATED TC8 AR841 WG62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12500101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOP TRANSFER RP1001 SCK60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12800001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04741</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thermal Top Phenol Free FSCT AP903 WG60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12884173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thermal PP 90 PP RP1002 WG62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12504163</x:t>
+    <x:t>01926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLUORO YELLOW AP04 SK60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12506030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RI-757/40 PP CAVITATED TC8 AP901 WG62</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -547,16 +451,16 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M15"/>
+  <x:dimension ref="A1:M4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="45.567768" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.567768" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.996339" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="9.282054" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="5.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="4.996339" style="0" customWidth="1"/>
@@ -623,10 +527,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>35000</x:v>
+        <x:v>28500</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>5040</x:v>
+        <x:v>4104</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
@@ -664,16 +568,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>28500</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5130</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>5</x:v>
@@ -693,28 +597,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>25000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>300</x:v>
+        <x:v>51000</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>5</x:v>
@@ -726,457 +630,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
-      <x:c r="A5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="G5" s="0">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
-      <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E6" s="0">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="G6" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:13">
-      <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E7" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>33000</x:v>
-      </x:c>
-      <x:c r="G7" s="0">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L7" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:13">
-      <x:c r="A8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F8" s="0">
-        <x:v>35400</x:v>
-      </x:c>
-      <x:c r="G8" s="0">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L8" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:13">
-      <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="G9" s="0">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:13">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F10" s="0">
-        <x:v>17000</x:v>
-      </x:c>
-      <x:c r="G10" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:13">
-      <x:c r="A11" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F11" s="0">
-        <x:v>80000</x:v>
-      </x:c>
-      <x:c r="G11" s="0">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:13">
-      <x:c r="A12" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="0">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="0">
-        <x:v>14000</x:v>
-      </x:c>
-      <x:c r="G12" s="0">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:13">
-      <x:c r="A13" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E13" s="0">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="0">
-        <x:v>33000</x:v>
-      </x:c>
-      <x:c r="G13" s="0">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J13" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:13">
-      <x:c r="A14" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E14" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F14" s="0">
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="G14" s="0">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L14" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:13">
-      <x:c r="A15" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E15" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F15" s="0">
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="G15" s="0">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L15" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M15" s="0">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
+++ b/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
@@ -55,7 +55,7 @@
     <x:t>Cantidad_Real</x:t>
   </x:si>
   <x:si>
-    <x:t>1045</x:t>
+    <x:t>1047</x:t>
   </x:si>
   <x:si>
     <x:t>00604</x:t>
@@ -67,25 +67,34 @@
     <x:t xml:space="preserve">Master    </x:t>
   </x:si>
   <x:si>
-    <x:t>12504010</x:t>
+    <x:t>12584010</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SU             </x:t>
   </x:si>
   <x:si>
-    <x:t>01926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLUORO YELLOW AP04 SK60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12506030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI-757/40 PP CAVITATED TC8 AP901 WG62</x:t>
+    <x:t>01573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RI MARK M 301 BLACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Graphics  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>12506396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00753-500 (RI-705/60 PP Gloss Clear TC8 AP900 WK135  SPL38  Sheet 500 mm  x 700 mm)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Resma     </x:t>
+  </x:si>
+  <x:si>
+    <x:t>12580101</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -456,11 +465,11 @@
   <x:cols>
     <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38.567768" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="79.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.567768" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="9.282054" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="5.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="4.996339" style="0" customWidth="1"/>
@@ -527,10 +536,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>28500</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4104</x:v>
+        <x:v>6912</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
@@ -562,25 +571,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>35000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>18</x:v>
@@ -597,31 +606,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>51000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
         <x:v>18</x:v>

--- a/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
+++ b/bin/Debug/net8.0-windows10.0.19041/ordenes_mp.xlsx
@@ -55,7 +55,7 @@
     <x:t>Cantidad_Real</x:t>
   </x:si>
   <x:si>
-    <x:t>1047</x:t>
+    <x:t>1048</x:t>
   </x:si>
   <x:si>
     <x:t>00604</x:t>
@@ -67,24 +67,12 @@
     <x:t xml:space="preserve">Master    </x:t>
   </x:si>
   <x:si>
-    <x:t>12584010</x:t>
+    <x:t>1450250140</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SU             </x:t>
   </x:si>
   <x:si>
-    <x:t>01573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RI MARK M 301 BLACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Graphics  </x:t>
-  </x:si>
-  <x:si>
-    <x:t>12506396</x:t>
-  </x:si>
-  <x:si>
     <x:t>00753</x:t>
   </x:si>
   <x:si>
@@ -94,7 +82,7 @@
     <x:t xml:space="preserve">Resma     </x:t>
   </x:si>
   <x:si>
-    <x:t>12580101</x:t>
+    <x:t>124010</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -460,7 +448,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M4"/>
+  <x:dimension ref="A1:M3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
@@ -470,7 +458,7 @@
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.853482" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.282054" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="5.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="4.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="9.567768" style="0" customWidth="1"/>
@@ -536,10 +524,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>48000</x:v>
+        <x:v>28500</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6912</x:v>
+        <x:v>4104</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
@@ -598,47 +586,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13">
-      <x:c r="A4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M4" s="0">
         <x:v>0</x:v>
       </x:c>
     </x:row>
